--- a/taskit.xlsx
+++ b/taskit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pekka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kapee\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F50E22FF-C88D-42C0-8360-9CB2519AE64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC2B368-4E01-4885-B1B2-A26CB6A5552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18180" yWindow="4200" windowWidth="21960" windowHeight="18180" xr2:uid="{4CB0A241-F6B9-478E-BB65-4B9F03381F4F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4CB0A241-F6B9-478E-BB65-4B9F03381F4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Taul1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="29">
   <si>
     <t>TEHTÄVÄLISTA SPL ja SPO</t>
   </si>
@@ -129,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,17 +608,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AEB630-55E5-4E0E-B093-54FE0D98D7C7}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1">
+    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C2" t="s">
         <v>1</v>
       </c>
@@ -632,7 +632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.5" customHeight="1" thickTop="1">
+    <row r="3" spans="1:6" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -652,12 +652,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.5" customHeight="1">
+    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -672,7 +672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1">
+    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -692,7 +692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.5" customHeight="1">
+    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -712,7 +712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="19.5" customHeight="1">
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1">
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -740,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.5" customHeight="1">
+    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -748,11 +748,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1">
+    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
@@ -766,11 +768,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="19.5" customHeight="1">
+    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
@@ -784,12 +788,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1">
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
         <v>1</v>
@@ -804,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1">
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -824,7 +828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1">
+    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -844,7 +848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1">
+    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -864,12 +868,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1">
+    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>1</v>
@@ -884,7 +888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1">
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -904,12 +908,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1">
+    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
         <v>1</v>
@@ -924,7 +928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1">
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -944,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1">
+    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -964,12 +968,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1">
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
         <v>1</v>
@@ -984,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1">
+    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1004,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1">
+    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1024,7 +1028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1">
+    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1044,15 +1048,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1">
+    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1060,13 +1064,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" thickBot="1">
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" thickTop="1"/>
+    <row r="28" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1074,6 +1078,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3923370c-5647-4f42-8697-36eb8b224da0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FAD15EC6B0214449900C342CAD696C17" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f43be529dfaaeb5c5f059a8b45c58c8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af" xmlns:ns3="3923370c-5647-4f42-8697-36eb8b224da0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db4d6064f0e2bd3072cf932d5a08d366" ns2:_="" ns3:_="">
     <xsd:import namespace="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af"/>
@@ -1268,34 +1292,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3923370c-5647-4f42-8697-36eb8b224da0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9346563-5540-4CB7-A9FE-3FCCE7907237}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A3A682-1F3D-4E8D-87D9-2691DADBE505}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932C4F21-A63A-4053-8836-E9F405DD97FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{932C4F21-A63A-4053-8836-E9F405DD97FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af"/>
+    <ds:schemaRef ds:uri="3923370c-5647-4f42-8697-36eb8b224da0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A3A682-1F3D-4E8D-87D9-2691DADBE505}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9346563-5540-4CB7-A9FE-3FCCE7907237}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af"/>
+    <ds:schemaRef ds:uri="3923370c-5647-4f42-8697-36eb8b224da0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/taskit.xlsx
+++ b/taskit.xlsx
@@ -1076,26 +1076,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3923370c-5647-4f42-8697-36eb8b224da0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FAD15EC6B0214449900C342CAD696C17" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f43be529dfaaeb5c5f059a8b45c58c8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af" xmlns:ns3="3923370c-5647-4f42-8697-36eb8b224da0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db4d6064f0e2bd3072cf932d5a08d366" ns2:_="" ns3:_="">
     <xsd:import namespace="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af"/>
@@ -1290,10 +1270,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3923370c-5647-4f42-8697-36eb8b224da0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A3A682-1F3D-4E8D-87D9-2691DADBE505}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9346563-5540-4CB7-A9FE-3FCCE7907237}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af"/>
+    <ds:schemaRef ds:uri="3923370c-5647-4f42-8697-36eb8b224da0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1310,20 +1321,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9346563-5540-4CB7-A9FE-3FCCE7907237}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A3A682-1F3D-4E8D-87D9-2691DADBE505}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b6e86e1a-7dac-4e5e-8694-d5f26c43e9af"/>
-    <ds:schemaRef ds:uri="3923370c-5647-4f42-8697-36eb8b224da0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>